--- a/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.DocumentReference.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.DocumentReference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3036" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="601">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -640,19 +640,39 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>DocumentReference.extension:homeCommunityId</t>
+  </si>
+  <si>
+    <t>homeCommunityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/ITI/MHD/StructureDefinition/ihe-HomeCommunityId}
+</t>
+  </si>
+  <si>
+    <t>The homeCommunityId where the artifact resides</t>
+  </si>
+  <si>
+    <t>The globally unique, immutable, identifier of the homeCommunityId entity where this artifact resides. The format of the value is an OID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>DocumentEntry.homeCommunityId</t>
+  </si>
+  <si>
     <t>DocumentReference.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -711,7 +731,7 @@
     <t>Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
+    <t xml:space="preserve">value:type}
 </t>
   </si>
   <si>
@@ -732,6 +752,24 @@
   <si>
     <t xml:space="preserve">Identifier {https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.EntryUUID.Identifier}
 </t>
+  </si>
+  <si>
+    <t>Business identifier for the DocumentReference</t>
+  </si>
+  <si>
+    <t>The Business identifier for the DocumentReference which maps to the DocumentEntry.entryUUID in XDS. This is used to refer to the DocumentReference itself as a record of the Document's metadata, as opposed to the UniqueId element which identifies the document which is pointed at by the document reference.</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier:uniqueId</t>
+  </si>
+  <si>
+    <t>uniqueId</t>
+  </si>
+  <si>
+    <t>Unique identifier for the referenced Document</t>
+  </si>
+  <si>
+    <t>The unique identifier for the referenced Document which maps to the DocumentEntry.uniqueId in XDS. This is used to identify the document which is pointed at by the DocumentReference Resource, as opposed to the entryUUID element which identifies the DocumentReference Resource itself. If this is present, then the identifier SHALL be the same as the one found in masterIdentifier.</t>
   </si>
   <si>
     <t>DocumentReference.status</t>
@@ -2179,12 +2217,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR75"/>
+  <dimension ref="A1:AR77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.13671875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.13671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -4256,7 +4294,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4278,14 +4316,12 @@
         <v>118</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4322,19 +4358,17 @@
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
@@ -4358,7 +4392,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4375,12 +4409,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4389,25 +4425,25 @@
         <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4458,7 +4494,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -4467,13 +4503,13 @@
         <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
@@ -4499,10 +4535,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4510,35 +4546,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4586,51 +4618,51 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4638,13 +4670,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
@@ -4653,16 +4685,20 @@
         <v>98</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4698,23 +4734,25 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
@@ -4723,40 +4761,38 @@
         <v>109</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AR20" t="s" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4777,13 +4813,13 @@
         <v>98</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4822,19 +4858,17 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -4849,69 +4883,69 @@
         <v>109</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AR21" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AO21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4936,11 +4970,13 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -4958,13 +4994,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4973,38 +5009,40 @@
         <v>109</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AR22" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AO22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP22" t="s" s="2">
+      <c r="B23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AQ22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AR22" t="s" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>83</v>
       </c>
@@ -5013,10 +5051,10 @@
         <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>83</v>
@@ -5025,17 +5063,15 @@
         <v>98</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5060,13 +5096,13 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -5084,13 +5120,13 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
@@ -5102,33 +5138,33 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5142,25 +5178,25 @@
         <v>97</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5186,13 +5222,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5210,10 +5244,10 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>97</v>
@@ -5225,50 +5259,50 @@
         <v>109</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>260</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>263</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>265</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>83</v>
@@ -5277,16 +5311,16 @@
         <v>98</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5312,13 +5346,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5336,13 +5370,13 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
@@ -5351,36 +5385,36 @@
         <v>109</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>271</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>275</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5403,15 +5437,17 @@
         <v>98</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5436,13 +5472,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>267</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5460,7 +5496,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -5475,44 +5511,44 @@
         <v>109</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>97</v>
@@ -5527,16 +5563,16 @@
         <v>98</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5562,13 +5598,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5586,13 +5622,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5601,36 +5637,36 @@
         <v>109</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5638,10 +5674,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>98</v>
@@ -5653,17 +5689,15 @@
         <v>98</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5712,13 +5746,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5727,40 +5761,40 @@
         <v>109</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5770,25 +5804,25 @@
         <v>97</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5838,7 +5872,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -5853,36 +5887,36 @@
         <v>109</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5893,28 +5927,28 @@
         <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5964,13 +5998,13 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -5979,36 +6013,36 @@
         <v>109</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6019,28 +6053,28 @@
         <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6090,13 +6124,13 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
@@ -6105,36 +6139,36 @@
         <v>109</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6157,15 +6191,17 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>112</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -6214,7 +6250,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>114</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6226,19 +6262,19 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>115</v>
+        <v>337</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6253,16 +6289,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6272,25 +6308,25 @@
         <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>120</v>
+        <v>341</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>121</v>
+        <v>342</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6340,7 +6376,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>125</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -6352,19 +6388,19 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>115</v>
+        <v>345</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6376,51 +6412,47 @@
         <v>83</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6468,19 +6500,19 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>114</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6492,7 +6524,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6509,21 +6541,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6532,19 +6564,19 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>119</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>120</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>345</v>
+        <v>121</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6570,13 +6602,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6594,31 +6626,31 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>125</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>350</v>
+        <v>115</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6630,47 +6662,51 @@
         <v>83</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>353</v>
+        <v>118</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6718,31 +6754,31 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>358</v>
+        <v>197</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6754,15 +6790,15 @@
         <v>83</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6770,7 +6806,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>97</v>
@@ -6785,20 +6821,18 @@
         <v>98</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6822,13 +6856,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6846,10 +6880,10 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>97</v>
@@ -6861,16 +6895,16 @@
         <v>109</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6879,18 +6913,18 @@
         <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6901,10 +6935,10 @@
         <v>97</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>83</v>
@@ -6913,20 +6947,16 @@
         <v>98</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6950,13 +6980,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6974,13 +7004,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6989,36 +7019,36 @@
         <v>109</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7026,7 +7056,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>97</v>
@@ -7041,16 +7071,20 @@
         <v>98</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -7098,13 +7132,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -7113,16 +7147,16 @@
         <v>109</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7131,18 +7165,18 @@
         <v>83</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7150,31 +7184,35 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>112</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -7198,13 +7236,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7222,62 +7260,62 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>114</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>115</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -7286,20 +7324,18 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>119</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7348,10 +7384,10 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>125</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>85</v>
@@ -7360,7 +7396,7 @@
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -7369,10 +7405,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>115</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7389,46 +7425,42 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7476,19 +7508,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>114</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7500,7 +7532,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7517,21 +7549,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7540,18 +7572,20 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>387</v>
+        <v>118</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>119</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7600,19 +7634,19 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>125</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7621,62 +7655,66 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7724,19 +7762,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>114</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7748,7 +7786,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7765,21 +7803,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7788,20 +7826,18 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>118</v>
+        <v>399</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>119</v>
+        <v>400</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7838,31 +7874,31 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>125</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7871,30 +7907,30 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>115</v>
+        <v>394</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7902,7 +7938,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>97</v>
@@ -7914,21 +7950,19 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>112</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>113</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>399</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7940,7 +7974,7 @@
         <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -7952,13 +7986,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7976,7 +8010,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>84</v>
@@ -7988,10 +8022,10 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
@@ -8000,7 +8034,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>405</v>
+        <v>115</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -8009,13 +8043,13 @@
         <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>407</v>
       </c>
@@ -8024,37 +8058,37 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>119</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -8066,7 +8100,7 @@
         <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>83</v>
@@ -8078,46 +8112,46 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>125</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
@@ -8126,7 +8160,7 @@
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>414</v>
+        <v>115</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8143,10 +8177,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8154,10 +8188,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -8166,22 +8200,20 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>416</v>
+        <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8194,7 +8226,7 @@
         <v>83</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>83</v>
@@ -8206,13 +8238,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -8230,7 +8262,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8245,7 +8277,7 @@
         <v>109</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
@@ -8254,7 +8286,7 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8263,18 +8295,18 @@
         <v>83</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8288,7 +8320,7 @@
         <v>97</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>83</v>
@@ -8297,19 +8329,17 @@
         <v>98</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>425</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8322,7 +8352,7 @@
         <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>83</v>
@@ -8334,13 +8364,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8358,7 +8388,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8373,7 +8403,7 @@
         <v>109</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>83</v>
@@ -8382,7 +8412,7 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8391,7 +8421,7 @@
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>83</v>
@@ -8399,10 +8429,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8413,7 +8443,7 @@
         <v>84</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -8422,22 +8452,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8486,7 +8516,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -8501,7 +8531,7 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8510,7 +8540,7 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8519,7 +8549,7 @@
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>83</v>
@@ -8527,10 +8557,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8538,7 +8568,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>97</v>
@@ -8553,19 +8583,19 @@
         <v>98</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8578,7 +8608,7 @@
         <v>83</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>83</v>
@@ -8614,7 +8644,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -8629,7 +8659,7 @@
         <v>109</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
@@ -8638,7 +8668,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8647,7 +8677,7 @@
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>83</v>
@@ -8655,10 +8685,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8681,17 +8711,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>111</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8704,7 +8736,7 @@
         <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>83</v>
@@ -8740,7 +8772,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
@@ -8755,7 +8787,7 @@
         <v>109</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
@@ -8764,7 +8796,7 @@
         <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8779,12 +8811,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8792,13 +8824,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>83</v>
@@ -8807,17 +8839,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8866,7 +8900,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -8881,7 +8915,7 @@
         <v>109</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
@@ -8890,7 +8924,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8905,12 +8939,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8918,13 +8952,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>83</v>
@@ -8933,18 +8967,18 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8956,7 +8990,7 @@
         <v>83</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>83</v>
@@ -8968,11 +9002,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8990,7 +9026,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>84</v>
@@ -9005,36 +9041,36 @@
         <v>109</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR54" t="s" s="2">
+      <c r="B55" t="s" s="2">
         <v>472</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9048,7 +9084,7 @@
         <v>97</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>83</v>
@@ -9057,18 +9093,18 @@
         <v>98</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -9116,7 +9152,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -9131,7 +9167,7 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -9140,27 +9176,27 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9168,30 +9204,32 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>112</v>
+        <v>480</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9216,13 +9254,11 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>83</v>
+        <v>483</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9240,7 +9276,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>114</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>84</v>
@@ -9252,22 +9288,22 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>115</v>
+        <v>394</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>83</v>
+        <v>486</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9276,26 +9312,26 @@
         <v>83</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -9304,19 +9340,19 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>119</v>
+        <v>488</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>120</v>
+        <v>489</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>121</v>
+        <v>490</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9366,19 +9402,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>125</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -9390,7 +9426,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>115</v>
+        <v>491</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9407,46 +9443,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -9494,19 +9526,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>341</v>
+        <v>114</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -9518,7 +9550,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9535,14 +9567,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9561,15 +9593,17 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>484</v>
+        <v>118</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>119</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9618,7 +9652,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>125</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -9630,25 +9664,25 @@
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>490</v>
+        <v>115</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>491</v>
+        <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -9659,14 +9693,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9679,24 +9713,26 @@
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>493</v>
+        <v>350</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>494</v>
+        <v>351</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9720,13 +9756,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>496</v>
+        <v>83</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>497</v>
+        <v>83</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9744,7 +9780,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>492</v>
+        <v>353</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -9756,19 +9792,19 @@
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>498</v>
+        <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>499</v>
+        <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>500</v>
+        <v>197</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9780,15 +9816,15 @@
         <v>83</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>498</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9799,25 +9835,25 @@
         <v>84</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9868,13 +9904,13 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
@@ -9883,36 +9919,36 @@
         <v>109</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>83</v>
+        <v>503</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9923,7 +9959,7 @@
         <v>84</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9935,15 +9971,17 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>112</v>
+        <v>505</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9968,13 +10006,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9992,31 +10030,31 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>114</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>511</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>115</v>
+        <v>512</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -10028,48 +10066,46 @@
         <v>83</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>118</v>
+        <v>514</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>119</v>
+        <v>515</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10106,31 +10142,31 @@
         <v>83</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>125</v>
+        <v>513</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -10139,13 +10175,13 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>115</v>
+        <v>518</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
@@ -10154,15 +10190,15 @@
         <v>83</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10182,20 +10218,18 @@
         <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>461</v>
+        <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>512</v>
+        <v>112</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10244,7 +10278,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>515</v>
+        <v>114</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10253,13 +10287,13 @@
         <v>97</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>516</v>
+        <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
@@ -10268,7 +10302,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>518</v>
+        <v>115</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10277,7 +10311,7 @@
         <v>83</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>83</v>
@@ -10285,21 +10319,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
@@ -10308,27 +10342,25 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>118</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>521</v>
+        <v>119</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>522</v>
+        <v>120</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>523</v>
+        <v>121</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>524</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>83</v>
       </c>
@@ -10360,34 +10392,34 @@
         <v>83</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>525</v>
+        <v>125</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>516</v>
+        <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>526</v>
+        <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -10396,7 +10428,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>527</v>
+        <v>115</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10405,18 +10437,18 @@
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10424,30 +10456,32 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K66" t="s" s="2">
-        <v>250</v>
+        <v>473</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10472,13 +10506,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>532</v>
+        <v>83</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10496,7 +10530,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -10505,42 +10539,42 @@
         <v>97</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>83</v>
+        <v>528</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>537</v>
+        <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10548,39 +10582,39 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K67" t="s" s="2">
-        <v>250</v>
+        <v>473</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10600,13 +10634,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10624,7 +10658,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -10633,42 +10667,42 @@
         <v>97</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>83</v>
+        <v>528</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>83</v>
+        <v>540</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10691,13 +10725,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>547</v>
+        <v>262</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10724,13 +10758,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>83</v>
+        <v>544</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10748,7 +10782,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>84</v>
@@ -10763,19 +10797,19 @@
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>83</v>
+        <v>546</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>282</v>
+        <v>547</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>283</v>
+        <v>548</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>284</v>
+        <v>549</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10784,15 +10818,15 @@
         <v>83</v>
       </c>
       <c r="AR68" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>550</v>
       </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10800,13 +10834,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>83</v>
@@ -10815,16 +10849,20 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>112</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10848,13 +10886,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10872,7 +10910,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>114</v>
+        <v>550</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>84</v>
@@ -10884,22 +10922,22 @@
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>115</v>
+        <v>548</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10908,29 +10946,29 @@
         <v>83</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>83</v>
@@ -10939,17 +10977,15 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>118</v>
+        <v>559</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>119</v>
+        <v>560</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10986,31 +11022,31 @@
         <v>83</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>125</v>
+        <v>558</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -11019,13 +11055,13 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -11034,15 +11070,15 @@
         <v>83</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>83</v>
+        <v>562</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11062,20 +11098,18 @@
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11124,7 +11158,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>557</v>
+        <v>114</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11133,13 +11167,13 @@
         <v>97</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>558</v>
+        <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>559</v>
+        <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>83</v>
@@ -11148,7 +11182,7 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11165,21 +11199,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
@@ -11188,19 +11222,19 @@
         <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>561</v>
+        <v>119</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>562</v>
+        <v>120</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>563</v>
+        <v>121</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11226,43 +11260,43 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>564</v>
+        <v>83</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>565</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>566</v>
+        <v>125</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11274,7 +11308,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11291,10 +11325,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11317,16 +11351,16 @@
         <v>98</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>219</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11376,7 +11410,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>84</v>
@@ -11385,13 +11419,13 @@
         <v>97</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>83</v>
+        <v>570</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>83</v>
@@ -11400,7 +11434,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>573</v>
+        <v>197</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11417,10 +11451,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11443,16 +11477,16 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11478,13 +11512,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11557,7 +11591,7 @@
         <v>84</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11566,19 +11600,19 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11628,13 +11662,13 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
@@ -11649,26 +11683,278 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AO75" t="s" s="2">
+      <c r="B76" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AP75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR75" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>588</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR75">
+  <autoFilter ref="A1:AR77">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11678,7 +11964,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.DocumentReference.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.Comprehensive.DocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
